--- a/ott_cinema_annual.xlsx
+++ b/ott_cinema_annual.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-1/BUSINESS^J ECONOMIC AND FINANCIAL DATA/Labs/BEFD_Labs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d9d1c894097c761c/Masaüstü/UNIPD/2-1/BUSINESS^J ECONOMIC AND FINANCIAL DATA/BEFD_Final_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{75089AAC-D6EB-4A74-9BC2-887DFA80168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6DCC8C7-7D61-4C71-9CA4-B25ECF60DA97}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{75089AAC-D6EB-4A74-9BC2-887DFA80168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC82939B-42C2-4021-946A-1B46D3B6E65B}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-8055" windowWidth="29040" windowHeight="15720" xr2:uid="{219BF2DB-FCDB-4EB8-A28F-26FA3E1A716D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{219BF2DB-FCDB-4EB8-A28F-26FA3E1A716D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Annual" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
